--- a/data/seq_reports/PIRE-Adu-Och-Sde-Sin_December2024_SeqSummary.xlsx
+++ b/data/seq_reports/PIRE-Adu-Och-Sde-Sin_December2024_SeqSummary.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tamucc-my.sharepoint.com/personal/chris_bird_tamucc_edu/Documents/GCL_2.0/Sequencing reports/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tamucc-my.sharepoint.com/personal/chris_bird_tamucc_edu/Documents/!students/Ty_Burris_Thesis/Data Analysis/och_cross-contam_testing/data/seq_reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{7BF48C50-76B2-4FB5-BE63-FD6C1459D9AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D86512B0-65C3-4935-BB2A-FF18C584CE1E}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{7BF48C50-76B2-4FB5-BE63-FD6C1459D9AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC6C3F7A-16F7-4BD0-9F68-A2A159C44B81}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8E2D2636-4E9D-4814-BC2C-FFFF638372C4}"/>
+    <workbookView xWindow="24975" yWindow="-28965" windowWidth="16440" windowHeight="28320" xr2:uid="{8E2D2636-4E9D-4814-BC2C-FFFF638372C4}"/>
   </bookViews>
   <sheets>
     <sheet name="qc.summary" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">qc.summary!$A$1:$O$715</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -2209,7 +2212,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -2691,7 +2694,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -3068,17 +3071,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2373588E-8E49-42A4-9373-CC2389CBBA35}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O715"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.41796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.83984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.83984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.26171875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3107,7 +3111,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>143</v>
       </c>
@@ -3138,7 +3142,7 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -3169,7 +3173,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>123</v>
       </c>
@@ -3200,7 +3204,7 @@
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>149</v>
       </c>
@@ -3229,7 +3233,7 @@
         <v>53.47</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -3258,7 +3262,7 @@
         <v>51.94</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -3287,7 +3291,7 @@
         <v>57.11</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>137</v>
       </c>
@@ -3316,7 +3320,7 @@
         <v>53.84</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>112</v>
       </c>
@@ -3345,7 +3349,7 @@
         <v>50.21</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>145</v>
       </c>
@@ -3374,7 +3378,7 @@
         <v>49.55</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -3403,7 +3407,7 @@
         <v>57.73</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>129</v>
       </c>
@@ -3432,7 +3436,7 @@
         <v>56.64</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -3461,7 +3465,7 @@
         <v>50.91</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>69</v>
       </c>
@@ -3490,7 +3494,7 @@
         <v>52.75</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -3519,7 +3523,7 @@
         <v>52.72</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>93</v>
       </c>
@@ -3548,7 +3552,7 @@
         <v>50.56</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>117</v>
       </c>
@@ -3577,7 +3581,7 @@
         <v>56.75</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -3606,7 +3610,7 @@
         <v>54.88</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>72</v>
       </c>
@@ -3635,7 +3639,7 @@
         <v>48.91</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>98</v>
       </c>
@@ -3664,7 +3668,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>157</v>
       </c>
@@ -3693,7 +3697,7 @@
         <v>51.85</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -3722,7 +3726,7 @@
         <v>53.29</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>68</v>
       </c>
@@ -3751,7 +3755,7 @@
         <v>50.95</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>165</v>
       </c>
@@ -3780,7 +3784,7 @@
         <v>57.01</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>139</v>
       </c>
@@ -3809,7 +3813,7 @@
         <v>61.62</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>97</v>
       </c>
@@ -3838,7 +3842,7 @@
         <v>53.48</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -3867,7 +3871,7 @@
         <v>57.7</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -3896,7 +3900,7 @@
         <v>57.08</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -3925,7 +3929,7 @@
         <v>52.22</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>111</v>
       </c>
@@ -3954,7 +3958,7 @@
         <v>51.47</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -3983,7 +3987,7 @@
         <v>48.17</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -4012,7 +4016,7 @@
         <v>50.51</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>43</v>
       </c>
@@ -4041,7 +4045,7 @@
         <v>51.65</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>156</v>
       </c>
@@ -4070,7 +4074,7 @@
         <v>59.88</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>84</v>
       </c>
@@ -4099,7 +4103,7 @@
         <v>50.21</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>102</v>
       </c>
@@ -4128,7 +4132,7 @@
         <v>49.15</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>134</v>
       </c>
@@ -4157,7 +4161,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>169</v>
       </c>
@@ -4186,7 +4190,7 @@
         <v>46.34</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>50</v>
       </c>
@@ -4215,7 +4219,7 @@
         <v>47.41</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>170</v>
       </c>
@@ -4244,7 +4248,7 @@
         <v>50.72</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>104</v>
       </c>
@@ -4273,7 +4277,7 @@
         <v>49.22</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>110</v>
       </c>
@@ -4302,7 +4306,7 @@
         <v>48.48</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>105</v>
       </c>
@@ -4331,7 +4335,7 @@
         <v>76.760000000000005</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>21</v>
       </c>
@@ -4360,7 +4364,7 @@
         <v>55.59</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>135</v>
       </c>
@@ -4389,7 +4393,7 @@
         <v>52.48</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>89</v>
       </c>
@@ -4418,7 +4422,7 @@
         <v>51.12</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>60</v>
       </c>
@@ -4447,7 +4451,7 @@
         <v>52.76</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>14</v>
       </c>
@@ -4476,7 +4480,7 @@
         <v>49.16</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -4505,7 +4509,7 @@
         <v>45.99</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>73</v>
       </c>
@@ -4534,7 +4538,7 @@
         <v>44.06</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>120</v>
       </c>
@@ -4563,7 +4567,7 @@
         <v>51.19</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>100</v>
       </c>
@@ -4592,7 +4596,7 @@
         <v>52.03</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>76</v>
       </c>
@@ -4621,7 +4625,7 @@
         <v>52.18</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>107</v>
       </c>
@@ -4650,7 +4654,7 @@
         <v>45.99</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>161</v>
       </c>
@@ -4679,7 +4683,7 @@
         <v>46.26</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>75</v>
       </c>
@@ -4708,7 +4712,7 @@
         <v>60.23</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>155</v>
       </c>
@@ -4737,7 +4741,7 @@
         <v>48.08</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>125</v>
       </c>
@@ -4766,7 +4770,7 @@
         <v>47.58</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>148</v>
       </c>
@@ -4795,7 +4799,7 @@
         <v>49.16</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>39</v>
       </c>
@@ -4824,7 +4828,7 @@
         <v>48.67</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>46</v>
       </c>
@@ -4853,7 +4857,7 @@
         <v>50.21</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -4882,7 +4886,7 @@
         <v>50.05</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>144</v>
       </c>
@@ -4911,7 +4915,7 @@
         <v>60.17</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>44</v>
       </c>
@@ -4940,7 +4944,7 @@
         <v>47.25</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>41</v>
       </c>
@@ -4969,7 +4973,7 @@
         <v>48.77</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>20</v>
       </c>
@@ -4998,7 +5002,7 @@
         <v>57.4</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>130</v>
       </c>
@@ -5027,7 +5031,7 @@
         <v>48.2</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>82</v>
       </c>
@@ -5056,7 +5060,7 @@
         <v>48.84</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>133</v>
       </c>
@@ -5085,7 +5089,7 @@
         <v>53.84</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>51</v>
       </c>
@@ -5114,7 +5118,7 @@
         <v>44.44</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>91</v>
       </c>
@@ -5143,7 +5147,7 @@
         <v>51.14</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>146</v>
       </c>
@@ -5172,7 +5176,7 @@
         <v>45.82</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>131</v>
       </c>
@@ -5201,7 +5205,7 @@
         <v>55.64</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -5230,7 +5234,7 @@
         <v>48.36</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>108</v>
       </c>
@@ -5259,7 +5263,7 @@
         <v>48.48</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>109</v>
       </c>
@@ -5288,7 +5292,7 @@
         <v>46.96</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>53</v>
       </c>
@@ -5317,7 +5321,7 @@
         <v>46.7</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>37</v>
       </c>
@@ -5346,7 +5350,7 @@
         <v>48.15</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>13</v>
       </c>
@@ -5375,7 +5379,7 @@
         <v>43.83</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>42</v>
       </c>
@@ -5404,7 +5408,7 @@
         <v>49.79</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>138</v>
       </c>
@@ -5433,7 +5437,7 @@
         <v>69.53</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>28</v>
       </c>
@@ -5462,7 +5466,7 @@
         <v>56.43</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>106</v>
       </c>
@@ -5491,7 +5495,7 @@
         <v>52.14</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>140</v>
       </c>
@@ -5520,7 +5524,7 @@
         <v>76.67</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>94</v>
       </c>
@@ -5549,7 +5553,7 @@
         <v>48.85</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>77</v>
       </c>
@@ -5578,7 +5582,7 @@
         <v>50.44</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>30</v>
       </c>
@@ -5607,7 +5611,7 @@
         <v>53.84</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>115</v>
       </c>
@@ -5636,7 +5640,7 @@
         <v>43.07</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>49</v>
       </c>
@@ -5665,7 +5669,7 @@
         <v>48.34</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>673</v>
       </c>
@@ -5694,7 +5698,7 @@
         <v>46.58</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
         <v>679</v>
       </c>
@@ -5723,7 +5727,7 @@
         <v>50.73</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
         <v>604</v>
       </c>
@@ -5752,7 +5756,7 @@
         <v>47.37</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>480</v>
       </c>
@@ -5781,7 +5785,7 @@
         <v>54.91</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>536</v>
       </c>
@@ -5810,7 +5814,7 @@
         <v>54.84</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>576</v>
       </c>
@@ -5839,7 +5843,7 @@
         <v>49.95</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>585</v>
       </c>
@@ -5868,7 +5872,7 @@
         <v>49.55</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>493</v>
       </c>
@@ -5897,7 +5901,7 @@
         <v>43.45</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>523</v>
       </c>
@@ -5926,7 +5930,7 @@
         <v>47.01</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>506</v>
       </c>
@@ -5955,7 +5959,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>495</v>
       </c>
@@ -5984,7 +5988,7 @@
         <v>46.68</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
         <v>707</v>
       </c>
@@ -6013,7 +6017,7 @@
         <v>46.14</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
         <v>527</v>
       </c>
@@ -6042,7 +6046,7 @@
         <v>47.32</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
         <v>671</v>
       </c>
@@ -6071,7 +6075,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>614</v>
       </c>
@@ -6100,7 +6104,7 @@
         <v>53.59</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
         <v>623</v>
       </c>
@@ -6129,7 +6133,7 @@
         <v>50.67</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
         <v>684</v>
       </c>
@@ -6158,7 +6162,7 @@
         <v>49.45</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
         <v>661</v>
       </c>
@@ -6187,7 +6191,7 @@
         <v>47.9</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
         <v>635</v>
       </c>
@@ -6216,7 +6220,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
         <v>718</v>
       </c>
@@ -6245,7 +6249,7 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
         <v>552</v>
       </c>
@@ -6274,7 +6278,7 @@
         <v>48.68</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
         <v>649</v>
       </c>
@@ -6303,7 +6307,7 @@
         <v>48.42</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
         <v>534</v>
       </c>
@@ -6332,7 +6336,7 @@
         <v>48.87</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
         <v>666</v>
       </c>
@@ -6361,7 +6365,7 @@
         <v>50.55</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
         <v>499</v>
       </c>
@@ -6390,7 +6394,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
         <v>541</v>
       </c>
@@ -6419,7 +6423,7 @@
         <v>50.22</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
         <v>683</v>
       </c>
@@ -6448,7 +6452,7 @@
         <v>48.5</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
         <v>657</v>
       </c>
@@ -6477,7 +6481,7 @@
         <v>52.15</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
         <v>692</v>
       </c>
@@ -6506,7 +6510,7 @@
         <v>48.76</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
         <v>572</v>
       </c>
@@ -6535,7 +6539,7 @@
         <v>46.35</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
         <v>486</v>
       </c>
@@ -6564,7 +6568,7 @@
         <v>48.63</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
         <v>667</v>
       </c>
@@ -6593,7 +6597,7 @@
         <v>46.71</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
         <v>719</v>
       </c>
@@ -6622,7 +6626,7 @@
         <v>48.36</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
         <v>570</v>
       </c>
@@ -6651,7 +6655,7 @@
         <v>49.65</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
         <v>696</v>
       </c>
@@ -6680,7 +6684,7 @@
         <v>46.87</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
         <v>710</v>
       </c>
@@ -6709,7 +6713,7 @@
         <v>46.93</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
         <v>532</v>
       </c>
@@ -6738,7 +6742,7 @@
         <v>47.29</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
         <v>478</v>
       </c>
@@ -6767,7 +6771,7 @@
         <v>46.57</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
         <v>535</v>
       </c>
@@ -6796,7 +6800,7 @@
         <v>50.77</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
         <v>620</v>
       </c>
@@ -6825,7 +6829,7 @@
         <v>45.61</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
         <v>482</v>
       </c>
@@ -6854,7 +6858,7 @@
         <v>46.91</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
         <v>602</v>
       </c>
@@ -6883,7 +6887,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
         <v>637</v>
       </c>
@@ -6912,7 +6916,7 @@
         <v>47.49</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
         <v>503</v>
       </c>
@@ -6941,7 +6945,7 @@
         <v>47.85</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
         <v>498</v>
       </c>
@@ -6970,7 +6974,7 @@
         <v>47.32</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
         <v>687</v>
       </c>
@@ -6999,7 +7003,7 @@
         <v>45.8</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
         <v>639</v>
       </c>
@@ -7028,7 +7032,7 @@
         <v>47.33</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
         <v>596</v>
       </c>
@@ -7057,7 +7061,7 @@
         <v>54.86</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
         <v>603</v>
       </c>
@@ -7086,7 +7090,7 @@
         <v>48.72</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
         <v>553</v>
       </c>
@@ -7115,7 +7119,7 @@
         <v>48.04</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
         <v>567</v>
       </c>
@@ -7144,7 +7148,7 @@
         <v>48.48</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
         <v>660</v>
       </c>
@@ -7173,7 +7177,7 @@
         <v>52.36</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
         <v>601</v>
       </c>
@@ -7202,7 +7206,7 @@
         <v>51.84</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
         <v>546</v>
       </c>
@@ -7231,7 +7235,7 @@
         <v>48.25</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
         <v>525</v>
       </c>
@@ -7260,7 +7264,7 @@
         <v>47.88</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
         <v>695</v>
       </c>
@@ -7289,7 +7293,7 @@
         <v>51.11</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" t="s">
         <v>514</v>
       </c>
@@ -7318,7 +7322,7 @@
         <v>48.95</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" t="s">
         <v>580</v>
       </c>
@@ -7347,7 +7351,7 @@
         <v>46.94</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" t="s">
         <v>551</v>
       </c>
@@ -7376,7 +7380,7 @@
         <v>50.09</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" t="s">
         <v>487</v>
       </c>
@@ -7405,7 +7409,7 @@
         <v>49.55</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" t="s">
         <v>538</v>
       </c>
@@ -7434,7 +7438,7 @@
         <v>44.91</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" t="s">
         <v>682</v>
       </c>
@@ -7463,7 +7467,7 @@
         <v>49.77</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" t="s">
         <v>526</v>
       </c>
@@ -7492,7 +7496,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" t="s">
         <v>587</v>
       </c>
@@ -7521,7 +7525,7 @@
         <v>49.81</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" t="s">
         <v>668</v>
       </c>
@@ -7550,7 +7554,7 @@
         <v>48.07</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" t="s">
         <v>617</v>
       </c>
@@ -7579,7 +7583,7 @@
         <v>47.23</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" t="s">
         <v>636</v>
       </c>
@@ -7608,7 +7612,7 @@
         <v>48.09</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" t="s">
         <v>641</v>
       </c>
@@ -7637,7 +7641,7 @@
         <v>47.31</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" t="s">
         <v>497</v>
       </c>
@@ -7666,7 +7670,7 @@
         <v>47.43</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" t="s">
         <v>622</v>
       </c>
@@ -7695,7 +7699,7 @@
         <v>51.92</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" t="s">
         <v>632</v>
       </c>
@@ -7724,7 +7728,7 @@
         <v>47.77</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" t="s">
         <v>640</v>
       </c>
@@ -7753,7 +7757,7 @@
         <v>50.13</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" t="s">
         <v>664</v>
       </c>
@@ -7782,7 +7786,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" t="s">
         <v>582</v>
       </c>
@@ -7811,7 +7815,7 @@
         <v>54.63</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" t="s">
         <v>505</v>
       </c>
@@ -7840,7 +7844,7 @@
         <v>46.65</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" t="s">
         <v>703</v>
       </c>
@@ -7869,7 +7873,7 @@
         <v>48.7</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" t="s">
         <v>599</v>
       </c>
@@ -7898,7 +7902,7 @@
         <v>51.56</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" t="s">
         <v>690</v>
       </c>
@@ -7927,7 +7931,7 @@
         <v>49.98</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" t="s">
         <v>483</v>
       </c>
@@ -7956,7 +7960,7 @@
         <v>47.72</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" t="s">
         <v>562</v>
       </c>
@@ -7985,7 +7989,7 @@
         <v>48.52</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" t="s">
         <v>568</v>
       </c>
@@ -8014,7 +8018,7 @@
         <v>48.26</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" t="s">
         <v>512</v>
       </c>
@@ -8043,7 +8047,7 @@
         <v>48.38</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" t="s">
         <v>672</v>
       </c>
@@ -8072,7 +8076,7 @@
         <v>50.33</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" t="s">
         <v>561</v>
       </c>
@@ -8101,7 +8105,7 @@
         <v>54.29</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" t="s">
         <v>509</v>
       </c>
@@ -8130,7 +8134,7 @@
         <v>50.44</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" t="s">
         <v>715</v>
       </c>
@@ -8159,7 +8163,7 @@
         <v>48.78</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" t="s">
         <v>583</v>
       </c>
@@ -8188,7 +8192,7 @@
         <v>48.74</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" t="s">
         <v>519</v>
       </c>
@@ -8217,7 +8221,7 @@
         <v>48.87</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" t="s">
         <v>511</v>
       </c>
@@ -8246,7 +8250,7 @@
         <v>49.72</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" t="s">
         <v>555</v>
       </c>
@@ -8275,7 +8279,7 @@
         <v>51.67</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" t="s">
         <v>655</v>
       </c>
@@ -8304,7 +8308,7 @@
         <v>49.01</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" t="s">
         <v>654</v>
       </c>
@@ -8333,7 +8337,7 @@
         <v>49.13</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" t="s">
         <v>624</v>
       </c>
@@ -8362,7 +8366,7 @@
         <v>48.44</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" t="s">
         <v>630</v>
       </c>
@@ -8391,7 +8395,7 @@
         <v>52.13</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" t="s">
         <v>491</v>
       </c>
@@ -8420,7 +8424,7 @@
         <v>52.37</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" t="s">
         <v>651</v>
       </c>
@@ -8449,7 +8453,7 @@
         <v>50.52</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" t="s">
         <v>594</v>
       </c>
@@ -8478,7 +8482,7 @@
         <v>50.79</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" t="s">
         <v>709</v>
       </c>
@@ -8507,7 +8511,7 @@
         <v>49.84</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" t="s">
         <v>558</v>
       </c>
@@ -8536,7 +8540,7 @@
         <v>50.26</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" t="s">
         <v>633</v>
       </c>
@@ -8565,7 +8569,7 @@
         <v>49.93</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" t="s">
         <v>589</v>
       </c>
@@ -8594,7 +8598,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" t="s">
         <v>645</v>
       </c>
@@ -8623,7 +8627,7 @@
         <v>51.53</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" t="s">
         <v>686</v>
       </c>
@@ -8652,7 +8656,7 @@
         <v>45.27</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" t="s">
         <v>656</v>
       </c>
@@ -8681,7 +8685,7 @@
         <v>43.81</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" t="s">
         <v>713</v>
       </c>
@@ -8710,7 +8714,7 @@
         <v>45.29</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" t="s">
         <v>670</v>
       </c>
@@ -8739,7 +8743,7 @@
         <v>44.49</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" t="s">
         <v>559</v>
       </c>
@@ -8768,7 +8772,7 @@
         <v>44.01</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" t="s">
         <v>608</v>
       </c>
@@ -8797,7 +8801,7 @@
         <v>47.23</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" t="s">
         <v>586</v>
       </c>
@@ -8826,7 +8830,7 @@
         <v>46.4</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" t="s">
         <v>658</v>
       </c>
@@ -8855,7 +8859,7 @@
         <v>44.01</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" t="s">
         <v>496</v>
       </c>
@@ -8884,7 +8888,7 @@
         <v>45.63</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" t="s">
         <v>678</v>
       </c>
@@ -8913,7 +8917,7 @@
         <v>46.08</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" t="s">
         <v>591</v>
       </c>
@@ -8942,7 +8946,7 @@
         <v>45.33</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" t="s">
         <v>677</v>
       </c>
@@ -8971,7 +8975,7 @@
         <v>47.29</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" t="s">
         <v>688</v>
       </c>
@@ -9000,7 +9004,7 @@
         <v>47.58</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" t="s">
         <v>680</v>
       </c>
@@ -9029,7 +9033,7 @@
         <v>48.51</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" t="s">
         <v>721</v>
       </c>
@@ -9058,7 +9062,7 @@
         <v>46.09</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" t="s">
         <v>560</v>
       </c>
@@ -9087,7 +9091,7 @@
         <v>45.31</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" t="s">
         <v>720</v>
       </c>
@@ -9116,7 +9120,7 @@
         <v>44.15</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" t="s">
         <v>607</v>
       </c>
@@ -9145,7 +9149,7 @@
         <v>46.84</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" t="s">
         <v>652</v>
       </c>
@@ -9174,7 +9178,7 @@
         <v>54.65</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" t="s">
         <v>597</v>
       </c>
@@ -9203,7 +9207,7 @@
         <v>47.46</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" t="s">
         <v>544</v>
       </c>
@@ -9232,7 +9236,7 @@
         <v>45.79</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" t="s">
         <v>648</v>
       </c>
@@ -9261,7 +9265,7 @@
         <v>45.08</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" t="s">
         <v>542</v>
       </c>
@@ -9290,7 +9294,7 @@
         <v>45.6</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" t="s">
         <v>550</v>
       </c>
@@ -9319,7 +9323,7 @@
         <v>48.97</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" t="s">
         <v>595</v>
       </c>
@@ -9348,7 +9352,7 @@
         <v>46.89</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" t="s">
         <v>702</v>
       </c>
@@ -9377,7 +9381,7 @@
         <v>48.96</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" t="s">
         <v>615</v>
       </c>
@@ -9406,7 +9410,7 @@
         <v>47.21</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A219" t="s">
         <v>722</v>
       </c>
@@ -9435,7 +9439,7 @@
         <v>47.45</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" t="s">
         <v>575</v>
       </c>
@@ -9464,7 +9468,7 @@
         <v>45.85</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" t="s">
         <v>507</v>
       </c>
@@ -9493,7 +9497,7 @@
         <v>46.31</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" t="s">
         <v>665</v>
       </c>
@@ -9522,7 +9526,7 @@
         <v>49.75</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" t="s">
         <v>592</v>
       </c>
@@ -9551,7 +9555,7 @@
         <v>47.45</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" t="s">
         <v>504</v>
       </c>
@@ -9580,7 +9584,7 @@
         <v>45.95</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" t="s">
         <v>627</v>
       </c>
@@ -9609,7 +9613,7 @@
         <v>46.51</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" t="s">
         <v>706</v>
       </c>
@@ -9638,7 +9642,7 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" t="s">
         <v>588</v>
       </c>
@@ -9667,7 +9671,7 @@
         <v>46.32</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" t="s">
         <v>488</v>
       </c>
@@ -9696,7 +9700,7 @@
         <v>49.03</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" t="s">
         <v>522</v>
       </c>
@@ -9725,7 +9729,7 @@
         <v>47.15</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" t="s">
         <v>557</v>
       </c>
@@ -9754,7 +9758,7 @@
         <v>45.22</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" t="s">
         <v>699</v>
       </c>
@@ -9783,7 +9787,7 @@
         <v>46.61</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" t="s">
         <v>626</v>
       </c>
@@ -9812,7 +9816,7 @@
         <v>47.02</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" t="s">
         <v>490</v>
       </c>
@@ -9841,7 +9845,7 @@
         <v>45.69</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" t="s">
         <v>566</v>
       </c>
@@ -9870,7 +9874,7 @@
         <v>44.68</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" t="s">
         <v>581</v>
       </c>
@@ -9899,7 +9903,7 @@
         <v>46.31</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" t="s">
         <v>500</v>
       </c>
@@ -9928,7 +9932,7 @@
         <v>45.59</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" t="s">
         <v>517</v>
       </c>
@@ -9957,7 +9961,7 @@
         <v>48.01</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" t="s">
         <v>610</v>
       </c>
@@ -9986,7 +9990,7 @@
         <v>45.49</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" t="s">
         <v>510</v>
       </c>
@@ -10015,7 +10019,7 @@
         <v>47.63</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" t="s">
         <v>531</v>
       </c>
@@ -10044,7 +10048,7 @@
         <v>51.04</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" t="s">
         <v>501</v>
       </c>
@@ -10073,7 +10077,7 @@
         <v>54.71</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" t="s">
         <v>571</v>
       </c>
@@ -10102,7 +10106,7 @@
         <v>53.42</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" t="s">
         <v>612</v>
       </c>
@@ -10131,7 +10135,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" t="s">
         <v>513</v>
       </c>
@@ -10160,7 +10164,7 @@
         <v>61.15</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" t="s">
         <v>631</v>
       </c>
@@ -10189,7 +10193,7 @@
         <v>57.6</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" t="s">
         <v>556</v>
       </c>
@@ -10218,7 +10222,7 @@
         <v>57.4</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" t="s">
         <v>579</v>
       </c>
@@ -10247,7 +10251,7 @@
         <v>54.23</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" t="s">
         <v>659</v>
       </c>
@@ -10276,7 +10280,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" t="s">
         <v>629</v>
       </c>
@@ -10305,7 +10309,7 @@
         <v>57.77</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" t="s">
         <v>476</v>
       </c>
@@ -10334,7 +10338,7 @@
         <v>56.15</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" t="s">
         <v>593</v>
       </c>
@@ -10363,7 +10367,7 @@
         <v>53.99</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" t="s">
         <v>521</v>
       </c>
@@ -10392,7 +10396,7 @@
         <v>58.02</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" t="s">
         <v>613</v>
       </c>
@@ -10421,7 +10425,7 @@
         <v>60.61</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" t="s">
         <v>616</v>
       </c>
@@ -10450,7 +10454,7 @@
         <v>53.03</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" t="s">
         <v>676</v>
       </c>
@@ -10479,7 +10483,7 @@
         <v>47.75</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" t="s">
         <v>481</v>
       </c>
@@ -10508,7 +10512,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" t="s">
         <v>578</v>
       </c>
@@ -10537,7 +10541,7 @@
         <v>49.54</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" t="s">
         <v>584</v>
       </c>
@@ -10566,7 +10570,7 @@
         <v>59.07</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" t="s">
         <v>669</v>
       </c>
@@ -10595,7 +10599,7 @@
         <v>44.36</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A260" t="s">
         <v>662</v>
       </c>
@@ -10624,7 +10628,7 @@
         <v>44.9</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A261" t="s">
         <v>619</v>
       </c>
@@ -10653,7 +10657,7 @@
         <v>47.11</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A262" t="s">
         <v>563</v>
       </c>
@@ -10682,7 +10686,7 @@
         <v>53.62</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A263" t="s">
         <v>663</v>
       </c>
@@ -10711,7 +10715,7 @@
         <v>48.87</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A264" t="s">
         <v>565</v>
       </c>
@@ -10740,7 +10744,7 @@
         <v>46.92</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" t="s">
         <v>545</v>
       </c>
@@ -10769,7 +10773,7 @@
         <v>43.76</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A266" t="s">
         <v>697</v>
       </c>
@@ -10798,7 +10802,7 @@
         <v>45.79</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A267" t="s">
         <v>698</v>
       </c>
@@ -10827,7 +10831,7 @@
         <v>45.23</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A268" t="s">
         <v>598</v>
       </c>
@@ -10856,7 +10860,7 @@
         <v>57.99</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A269" t="s">
         <v>694</v>
       </c>
@@ -10885,7 +10889,7 @@
         <v>53.47</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A270" t="s">
         <v>642</v>
       </c>
@@ -10914,7 +10918,7 @@
         <v>53.24</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A271" t="s">
         <v>528</v>
       </c>
@@ -10943,7 +10947,7 @@
         <v>43.71</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A272" t="s">
         <v>485</v>
       </c>
@@ -10972,7 +10976,7 @@
         <v>49.69</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A273" t="s">
         <v>537</v>
       </c>
@@ -11001,7 +11005,7 @@
         <v>67.91</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A274" t="s">
         <v>609</v>
       </c>
@@ -11030,7 +11034,7 @@
         <v>50.57</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A275" t="s">
         <v>653</v>
       </c>
@@ -11059,7 +11063,7 @@
         <v>47.47</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A276" t="s">
         <v>533</v>
       </c>
@@ -11088,7 +11092,7 @@
         <v>41.97</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A277" t="s">
         <v>647</v>
       </c>
@@ -11117,7 +11121,7 @@
         <v>42.22</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A278" t="s">
         <v>494</v>
       </c>
@@ -11146,7 +11150,7 @@
         <v>52.55</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A279" t="s">
         <v>634</v>
       </c>
@@ -11175,7 +11179,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A280" t="s">
         <v>716</v>
       </c>
@@ -11204,7 +11208,7 @@
         <v>44.77</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A281" t="s">
         <v>516</v>
       </c>
@@ -11233,7 +11237,7 @@
         <v>49.89</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A282" t="s">
         <v>569</v>
       </c>
@@ -11262,7 +11266,7 @@
         <v>45.42</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A283" t="s">
         <v>714</v>
       </c>
@@ -11291,7 +11295,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A284" t="s">
         <v>693</v>
       </c>
@@ -11320,7 +11324,7 @@
         <v>51.48</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A285" t="s">
         <v>539</v>
       </c>
@@ -11349,7 +11353,7 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A286" t="s">
         <v>717</v>
       </c>
@@ -11378,7 +11382,7 @@
         <v>51.07</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A287" t="s">
         <v>520</v>
       </c>
@@ -11407,7 +11411,7 @@
         <v>48.61</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A288" t="s">
         <v>701</v>
       </c>
@@ -11436,7 +11440,7 @@
         <v>48.03</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A289" t="s">
         <v>618</v>
       </c>
@@ -11465,7 +11469,7 @@
         <v>48.49</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A290" t="s">
         <v>708</v>
       </c>
@@ -11494,7 +11498,7 @@
         <v>47.66</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A291" t="s">
         <v>700</v>
       </c>
@@ -11523,7 +11527,7 @@
         <v>47.07</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A292" t="s">
         <v>515</v>
       </c>
@@ -11552,7 +11556,7 @@
         <v>48.89</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A293" t="s">
         <v>543</v>
       </c>
@@ -11581,7 +11585,7 @@
         <v>48.9</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A294" t="s">
         <v>529</v>
       </c>
@@ -11610,7 +11614,7 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A295" t="s">
         <v>489</v>
       </c>
@@ -11639,7 +11643,7 @@
         <v>48.87</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A296" t="s">
         <v>691</v>
       </c>
@@ -11668,7 +11672,7 @@
         <v>45.68</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A297" t="s">
         <v>554</v>
       </c>
@@ -11697,7 +11701,7 @@
         <v>45.34</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A298" t="s">
         <v>644</v>
       </c>
@@ -11726,7 +11730,7 @@
         <v>47.4</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A299" t="s">
         <v>605</v>
       </c>
@@ -11755,7 +11759,7 @@
         <v>46.92</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A300" t="s">
         <v>502</v>
       </c>
@@ -11784,7 +11788,7 @@
         <v>45.51</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A301" t="s">
         <v>524</v>
       </c>
@@ -11813,7 +11817,7 @@
         <v>46.81</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A302" t="s">
         <v>564</v>
       </c>
@@ -11842,7 +11846,7 @@
         <v>46.38</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A303" t="s">
         <v>674</v>
       </c>
@@ -11871,7 +11875,7 @@
         <v>46.27</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A304" t="s">
         <v>705</v>
       </c>
@@ -11900,7 +11904,7 @@
         <v>45.09</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A305" t="s">
         <v>548</v>
       </c>
@@ -11929,7 +11933,7 @@
         <v>46.57</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A306" t="s">
         <v>712</v>
       </c>
@@ -11958,7 +11962,7 @@
         <v>47.07</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A307" t="s">
         <v>577</v>
       </c>
@@ -11987,7 +11991,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A308" t="s">
         <v>549</v>
       </c>
@@ -12016,7 +12020,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A309" t="s">
         <v>611</v>
       </c>
@@ -12045,7 +12049,7 @@
         <v>47.97</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A310" t="s">
         <v>530</v>
       </c>
@@ -12074,7 +12078,7 @@
         <v>48.32</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A311" t="s">
         <v>628</v>
       </c>
@@ -12103,7 +12107,7 @@
         <v>44.96</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A312" t="s">
         <v>621</v>
       </c>
@@ -12132,7 +12136,7 @@
         <v>44.96</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A313" t="s">
         <v>606</v>
       </c>
@@ -12161,7 +12165,7 @@
         <v>48.73</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A314" t="s">
         <v>681</v>
       </c>
@@ -12190,7 +12194,7 @@
         <v>49.12</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A315" t="s">
         <v>590</v>
       </c>
@@ -12219,7 +12223,7 @@
         <v>49.17</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A316" t="s">
         <v>704</v>
       </c>
@@ -12248,7 +12252,7 @@
         <v>49.53</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A317" t="s">
         <v>643</v>
       </c>
@@ -12277,7 +12281,7 @@
         <v>47.13</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A318" t="s">
         <v>484</v>
       </c>
@@ -12306,7 +12310,7 @@
         <v>49.26</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A319" t="s">
         <v>650</v>
       </c>
@@ -12335,7 +12339,7 @@
         <v>49.72</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A320" t="s">
         <v>508</v>
       </c>
@@ -12364,7 +12368,7 @@
         <v>47.19</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A321" t="s">
         <v>625</v>
       </c>
@@ -12393,7 +12397,7 @@
         <v>46.36</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A322" t="s">
         <v>547</v>
       </c>
@@ -12422,7 +12426,7 @@
         <v>48.4</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A323" t="s">
         <v>675</v>
       </c>
@@ -12451,7 +12455,7 @@
         <v>47.59</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A324" t="s">
         <v>711</v>
       </c>
@@ -12480,7 +12484,7 @@
         <v>46.95</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A325" t="s">
         <v>492</v>
       </c>
@@ -12509,7 +12513,7 @@
         <v>46.99</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A326" t="s">
         <v>685</v>
       </c>
@@ -12538,7 +12542,7 @@
         <v>50.02</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A327" t="s">
         <v>540</v>
       </c>
@@ -12567,7 +12571,7 @@
         <v>46.84</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A328" t="s">
         <v>479</v>
       </c>
@@ -12596,7 +12600,7 @@
         <v>43.9</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A329" t="s">
         <v>573</v>
       </c>
@@ -12625,7 +12629,7 @@
         <v>46.37</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A330" t="s">
         <v>600</v>
       </c>
@@ -12654,7 +12658,7 @@
         <v>45.24</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A331" t="s">
         <v>638</v>
       </c>
@@ -12683,7 +12687,7 @@
         <v>45.79</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A332" t="s">
         <v>574</v>
       </c>
@@ -12712,7 +12716,7 @@
         <v>44.08</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A333" t="s">
         <v>518</v>
       </c>
@@ -12741,7 +12745,7 @@
         <v>43.98</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A334" t="s">
         <v>689</v>
       </c>
@@ -12770,7 +12774,7 @@
         <v>44.51</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A335" t="s">
         <v>646</v>
       </c>
@@ -12799,7 +12803,7 @@
         <v>42.89</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A336" t="s">
         <v>288</v>
       </c>
@@ -12828,7 +12832,7 @@
         <v>47.32</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A337" t="s">
         <v>193</v>
       </c>
@@ -12857,7 +12861,7 @@
         <v>47.37</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A338" t="s">
         <v>390</v>
       </c>
@@ -12886,7 +12890,7 @@
         <v>47.94</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A339" t="s">
         <v>234</v>
       </c>
@@ -12915,7 +12919,7 @@
         <v>47.51</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A340" t="s">
         <v>228</v>
       </c>
@@ -12944,7 +12948,7 @@
         <v>46.24</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A341" t="s">
         <v>339</v>
       </c>
@@ -12973,7 +12977,7 @@
         <v>47.88</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A342" t="s">
         <v>375</v>
       </c>
@@ -13002,7 +13006,7 @@
         <v>48.72</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A343" t="s">
         <v>354</v>
       </c>
@@ -13031,7 +13035,7 @@
         <v>49.37</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A344" t="s">
         <v>206</v>
       </c>
@@ -13060,7 +13064,7 @@
         <v>48.89</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A345" t="s">
         <v>330</v>
       </c>
@@ -13089,7 +13093,7 @@
         <v>46.44</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A346" t="s">
         <v>454</v>
       </c>
@@ -13118,7 +13122,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A347" t="s">
         <v>247</v>
       </c>
@@ -13147,7 +13151,7 @@
         <v>47.57</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A348" t="s">
         <v>221</v>
       </c>
@@ -13176,7 +13180,7 @@
         <v>47.31</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A349" t="s">
         <v>211</v>
       </c>
@@ -13205,7 +13209,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A350" t="s">
         <v>199</v>
       </c>
@@ -13234,7 +13238,7 @@
         <v>47.4</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A351" t="s">
         <v>207</v>
       </c>
@@ -13263,7 +13267,7 @@
         <v>48.24</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A352" t="s">
         <v>430</v>
       </c>
@@ -13292,7 +13296,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A353" t="s">
         <v>348</v>
       </c>
@@ -13321,7 +13325,7 @@
         <v>47.58</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A354" t="s">
         <v>256</v>
       </c>
@@ -13350,7 +13354,7 @@
         <v>46.75</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A355" t="s">
         <v>315</v>
       </c>
@@ -13379,7 +13383,7 @@
         <v>49.39</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A356" t="s">
         <v>284</v>
       </c>
@@ -13408,7 +13412,7 @@
         <v>48.93</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A357" t="s">
         <v>474</v>
       </c>
@@ -13437,7 +13441,7 @@
         <v>48.96</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A358" t="s">
         <v>175</v>
       </c>
@@ -13466,7 +13470,7 @@
         <v>47.68</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A359" t="s">
         <v>188</v>
       </c>
@@ -13495,7 +13499,7 @@
         <v>47.46</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A360" t="s">
         <v>277</v>
       </c>
@@ -13524,7 +13528,7 @@
         <v>47.35</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A361" t="s">
         <v>215</v>
       </c>
@@ -13553,7 +13557,7 @@
         <v>46.26</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A362" t="s">
         <v>176</v>
       </c>
@@ -13582,7 +13586,7 @@
         <v>48.37</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A363" t="s">
         <v>410</v>
       </c>
@@ -13611,7 +13615,7 @@
         <v>46.79</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A364" t="s">
         <v>299</v>
       </c>
@@ -13640,7 +13644,7 @@
         <v>46.44</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A365" t="s">
         <v>467</v>
       </c>
@@ -13669,7 +13673,7 @@
         <v>46.96</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A366" t="s">
         <v>347</v>
       </c>
@@ -13698,7 +13702,7 @@
         <v>47.26</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A367" t="s">
         <v>291</v>
       </c>
@@ -13727,7 +13731,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A368" t="s">
         <v>209</v>
       </c>
@@ -13756,7 +13760,7 @@
         <v>47.26</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A369" t="s">
         <v>326</v>
       </c>
@@ -13785,7 +13789,7 @@
         <v>46.93</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A370" t="s">
         <v>318</v>
       </c>
@@ -13814,7 +13818,7 @@
         <v>47.82</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A371" t="s">
         <v>441</v>
       </c>
@@ -13843,7 +13847,7 @@
         <v>47.62</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A372" t="s">
         <v>433</v>
       </c>
@@ -13872,7 +13876,7 @@
         <v>49.08</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A373" t="s">
         <v>362</v>
       </c>
@@ -13901,7 +13905,7 @@
         <v>48.27</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A374" t="s">
         <v>333</v>
       </c>
@@ -13930,7 +13934,7 @@
         <v>46.65</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A375" t="s">
         <v>220</v>
       </c>
@@ -13959,7 +13963,7 @@
         <v>49.05</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A376" t="s">
         <v>421</v>
       </c>
@@ -13988,7 +13992,7 @@
         <v>48.4</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A377" t="s">
         <v>239</v>
       </c>
@@ -14017,7 +14021,7 @@
         <v>47.98</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A378" t="s">
         <v>232</v>
       </c>
@@ -14046,7 +14050,7 @@
         <v>48.05</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A379" t="s">
         <v>337</v>
       </c>
@@ -14075,7 +14079,7 @@
         <v>47.61</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A380" t="s">
         <v>407</v>
       </c>
@@ -14104,7 +14108,7 @@
         <v>48.69</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A381" t="s">
         <v>306</v>
       </c>
@@ -14133,7 +14137,7 @@
         <v>51.44</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A382" t="s">
         <v>303</v>
       </c>
@@ -14162,7 +14166,7 @@
         <v>46.83</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A383" t="s">
         <v>475</v>
       </c>
@@ -14191,7 +14195,7 @@
         <v>48.56</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A384" t="s">
         <v>242</v>
       </c>
@@ -14220,7 +14224,7 @@
         <v>47.81</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A385" t="s">
         <v>426</v>
       </c>
@@ -14249,7 +14253,7 @@
         <v>47.14</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A386" t="s">
         <v>370</v>
       </c>
@@ -14278,7 +14282,7 @@
         <v>46.42</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A387" t="s">
         <v>259</v>
       </c>
@@ -14307,7 +14311,7 @@
         <v>50.65</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A388" t="s">
         <v>356</v>
       </c>
@@ -14336,7 +14340,7 @@
         <v>50.27</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A389" t="s">
         <v>351</v>
       </c>
@@ -14365,7 +14369,7 @@
         <v>50.22</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A390" t="s">
         <v>459</v>
       </c>
@@ -14394,7 +14398,7 @@
         <v>49.06</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A391" t="s">
         <v>371</v>
       </c>
@@ -14423,7 +14427,7 @@
         <v>54.05</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A392" t="s">
         <v>471</v>
       </c>
@@ -14452,7 +14456,7 @@
         <v>48.85</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A393" t="s">
         <v>201</v>
       </c>
@@ -14481,7 +14485,7 @@
         <v>48.62</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A394" t="s">
         <v>468</v>
       </c>
@@ -14510,7 +14514,7 @@
         <v>50.54</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A395" t="s">
         <v>208</v>
       </c>
@@ -14539,7 +14543,7 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A396" t="s">
         <v>439</v>
       </c>
@@ -14568,7 +14572,7 @@
         <v>48.49</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A397" t="s">
         <v>466</v>
       </c>
@@ -14597,7 +14601,7 @@
         <v>50.42</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A398" t="s">
         <v>383</v>
       </c>
@@ -14626,7 +14630,7 @@
         <v>51.86</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A399" t="s">
         <v>472</v>
       </c>
@@ -14655,7 +14659,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A400" t="s">
         <v>360</v>
       </c>
@@ -14684,7 +14688,7 @@
         <v>51.11</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A401" t="s">
         <v>332</v>
       </c>
@@ -14713,7 +14717,7 @@
         <v>51.23</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A402" t="s">
         <v>275</v>
       </c>
@@ -14742,7 +14746,7 @@
         <v>50.52</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A403" t="s">
         <v>190</v>
       </c>
@@ -14771,7 +14775,7 @@
         <v>49.03</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A404" t="s">
         <v>432</v>
       </c>
@@ -14800,7 +14804,7 @@
         <v>55.68</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A405" t="s">
         <v>253</v>
       </c>
@@ -14829,7 +14833,7 @@
         <v>50.47</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A406" t="s">
         <v>385</v>
       </c>
@@ -14858,7 +14862,7 @@
         <v>51.31</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A407" t="s">
         <v>181</v>
       </c>
@@ -14887,7 +14891,7 @@
         <v>51.28</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A408" t="s">
         <v>462</v>
       </c>
@@ -14916,7 +14920,7 @@
         <v>49.58</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A409" t="s">
         <v>204</v>
       </c>
@@ -14945,7 +14949,7 @@
         <v>51.33</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A410" t="s">
         <v>344</v>
       </c>
@@ -14974,7 +14978,7 @@
         <v>49.45</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A411" t="s">
         <v>314</v>
       </c>
@@ -15003,7 +15007,7 @@
         <v>52.41</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A412" t="s">
         <v>436</v>
       </c>
@@ -15032,7 +15036,7 @@
         <v>51.36</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A413" t="s">
         <v>177</v>
       </c>
@@ -15061,7 +15065,7 @@
         <v>50.97</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A414" t="s">
         <v>336</v>
       </c>
@@ -15090,7 +15094,7 @@
         <v>52.34</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A415" t="s">
         <v>463</v>
       </c>
@@ -15119,7 +15123,7 @@
         <v>52.57</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A416" t="s">
         <v>289</v>
       </c>
@@ -15148,7 +15152,7 @@
         <v>50.77</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A417" t="s">
         <v>257</v>
       </c>
@@ -15177,7 +15181,7 @@
         <v>50.74</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A418" t="s">
         <v>427</v>
       </c>
@@ -15206,7 +15210,7 @@
         <v>49.42</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A419" t="s">
         <v>308</v>
       </c>
@@ -15235,7 +15239,7 @@
         <v>49.99</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A420" t="s">
         <v>458</v>
       </c>
@@ -15264,7 +15268,7 @@
         <v>50.55</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A421" t="s">
         <v>282</v>
       </c>
@@ -15293,7 +15297,7 @@
         <v>51.3</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A422" t="s">
         <v>194</v>
       </c>
@@ -15322,7 +15326,7 @@
         <v>47.58</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A423" t="s">
         <v>312</v>
       </c>
@@ -15351,7 +15355,7 @@
         <v>49.67</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A424" t="s">
         <v>416</v>
       </c>
@@ -15380,7 +15384,7 @@
         <v>49.73</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A425" t="s">
         <v>186</v>
       </c>
@@ -15409,7 +15413,7 @@
         <v>48.25</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A426" t="s">
         <v>424</v>
       </c>
@@ -15438,7 +15442,7 @@
         <v>48.32</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A427" t="s">
         <v>305</v>
       </c>
@@ -15467,7 +15471,7 @@
         <v>47.34</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A428" t="s">
         <v>387</v>
       </c>
@@ -15496,7 +15500,7 @@
         <v>48.95</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A429" t="s">
         <v>400</v>
       </c>
@@ -15525,7 +15529,7 @@
         <v>48.44</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A430" t="s">
         <v>448</v>
       </c>
@@ -15554,7 +15558,7 @@
         <v>48.34</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A431" t="s">
         <v>301</v>
       </c>
@@ -15583,7 +15587,7 @@
         <v>47.43</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A432" t="s">
         <v>286</v>
       </c>
@@ -15612,7 +15616,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A433" t="s">
         <v>369</v>
       </c>
@@ -15641,7 +15645,7 @@
         <v>47.84</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A434" t="s">
         <v>235</v>
       </c>
@@ -15670,7 +15674,7 @@
         <v>47.07</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A435" t="s">
         <v>272</v>
       </c>
@@ -15699,7 +15703,7 @@
         <v>48.32</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A436" t="s">
         <v>473</v>
       </c>
@@ -15728,7 +15732,7 @@
         <v>48.95</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A437" t="s">
         <v>367</v>
       </c>
@@ -15757,7 +15761,7 @@
         <v>48.65</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A438" t="s">
         <v>418</v>
       </c>
@@ -15786,7 +15790,7 @@
         <v>47.97</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A439" t="s">
         <v>319</v>
       </c>
@@ -15815,7 +15819,7 @@
         <v>49.01</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A440" t="s">
         <v>309</v>
       </c>
@@ -15844,7 +15848,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A441" t="s">
         <v>182</v>
       </c>
@@ -15873,7 +15877,7 @@
         <v>49.26</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A442" t="s">
         <v>363</v>
       </c>
@@ -15902,7 +15906,7 @@
         <v>49.44</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A443" t="s">
         <v>425</v>
       </c>
@@ -15931,7 +15935,7 @@
         <v>48.45</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A444" t="s">
         <v>173</v>
       </c>
@@ -15960,7 +15964,7 @@
         <v>47.77</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A445" t="s">
         <v>381</v>
       </c>
@@ -15989,7 +15993,7 @@
         <v>48.89</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A446" t="s">
         <v>423</v>
       </c>
@@ -16018,7 +16022,7 @@
         <v>48.22</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A447" t="s">
         <v>316</v>
       </c>
@@ -16047,7 +16051,7 @@
         <v>49.23</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A448" t="s">
         <v>402</v>
       </c>
@@ -16076,7 +16080,7 @@
         <v>48.39</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A449" t="s">
         <v>218</v>
       </c>
@@ -16105,7 +16109,7 @@
         <v>48.68</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A450" t="s">
         <v>353</v>
       </c>
@@ -16134,7 +16138,7 @@
         <v>48.37</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A451" t="s">
         <v>429</v>
       </c>
@@ -16163,7 +16167,7 @@
         <v>48.66</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A452" t="s">
         <v>205</v>
       </c>
@@ -16192,7 +16196,7 @@
         <v>49.37</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A453" t="s">
         <v>434</v>
       </c>
@@ -16221,7 +16225,7 @@
         <v>49.09</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A454" t="s">
         <v>379</v>
       </c>
@@ -16250,7 +16254,7 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A455" t="s">
         <v>460</v>
       </c>
@@ -16279,7 +16283,7 @@
         <v>49.83</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A456" t="s">
         <v>263</v>
       </c>
@@ -16308,7 +16312,7 @@
         <v>48.32</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A457" t="s">
         <v>374</v>
       </c>
@@ -16337,7 +16341,7 @@
         <v>48.21</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A458" t="s">
         <v>231</v>
       </c>
@@ -16366,7 +16370,7 @@
         <v>48.24</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A459" t="s">
         <v>465</v>
       </c>
@@ -16395,7 +16399,7 @@
         <v>48.71</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A460" t="s">
         <v>437</v>
       </c>
@@ -16424,7 +16428,7 @@
         <v>47.48</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A461" t="s">
         <v>236</v>
       </c>
@@ -16453,7 +16457,7 @@
         <v>49.08</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A462" t="s">
         <v>185</v>
       </c>
@@ -16482,7 +16486,7 @@
         <v>48.81</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A463" t="s">
         <v>270</v>
       </c>
@@ -16511,7 +16515,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A464" t="s">
         <v>413</v>
       </c>
@@ -16540,7 +16544,7 @@
         <v>52.12</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A465" t="s">
         <v>219</v>
       </c>
@@ -16569,7 +16573,7 @@
         <v>49.62</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A466" t="s">
         <v>285</v>
       </c>
@@ -16598,7 +16602,7 @@
         <v>48.65</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A467" t="s">
         <v>346</v>
       </c>
@@ -16627,7 +16631,7 @@
         <v>49.75</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A468" t="s">
         <v>317</v>
       </c>
@@ -16656,7 +16660,7 @@
         <v>51.18</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A469" t="s">
         <v>438</v>
       </c>
@@ -16685,7 +16689,7 @@
         <v>49.27</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A470" t="s">
         <v>386</v>
       </c>
@@ -16714,7 +16718,7 @@
         <v>49.75</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A471" t="s">
         <v>267</v>
       </c>
@@ -16743,7 +16747,7 @@
         <v>48.73</v>
       </c>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A472" t="s">
         <v>331</v>
       </c>
@@ -16772,7 +16776,7 @@
         <v>49.37</v>
       </c>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A473" t="s">
         <v>212</v>
       </c>
@@ -16801,7 +16805,7 @@
         <v>47.96</v>
       </c>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A474" t="s">
         <v>405</v>
       </c>
@@ -16830,7 +16834,7 @@
         <v>49.37</v>
       </c>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A475" t="s">
         <v>202</v>
       </c>
@@ -16859,7 +16863,7 @@
         <v>49.12</v>
       </c>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A476" t="s">
         <v>230</v>
       </c>
@@ -16888,7 +16892,7 @@
         <v>46.18</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A477" t="s">
         <v>382</v>
       </c>
@@ -16917,7 +16921,7 @@
         <v>44.52</v>
       </c>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A478" t="s">
         <v>341</v>
       </c>
@@ -16946,7 +16950,7 @@
         <v>45.77</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A479" t="s">
         <v>189</v>
       </c>
@@ -16975,7 +16979,7 @@
         <v>44.69</v>
       </c>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A480" t="s">
         <v>324</v>
       </c>
@@ -17004,7 +17008,7 @@
         <v>45.8</v>
       </c>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A481" t="s">
         <v>279</v>
       </c>
@@ -17033,7 +17037,7 @@
         <v>42.21</v>
       </c>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A482" t="s">
         <v>213</v>
       </c>
@@ -17062,7 +17066,7 @@
         <v>41.93</v>
       </c>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A483" t="s">
         <v>261</v>
       </c>
@@ -17091,7 +17095,7 @@
         <v>46.27</v>
       </c>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A484" t="s">
         <v>340</v>
       </c>
@@ -17120,7 +17124,7 @@
         <v>44.35</v>
       </c>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A485" t="s">
         <v>378</v>
       </c>
@@ -17149,7 +17153,7 @@
         <v>44.86</v>
       </c>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A486" t="s">
         <v>271</v>
       </c>
@@ -17178,7 +17182,7 @@
         <v>46.52</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A487" t="s">
         <v>395</v>
       </c>
@@ -17207,7 +17211,7 @@
         <v>41.71</v>
       </c>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A488" t="s">
         <v>321</v>
       </c>
@@ -17236,7 +17240,7 @@
         <v>46.73</v>
       </c>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A489" t="s">
         <v>453</v>
       </c>
@@ -17265,7 +17269,7 @@
         <v>45.79</v>
       </c>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A490" t="s">
         <v>412</v>
       </c>
@@ -17294,7 +17298,7 @@
         <v>45.13</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A491" t="s">
         <v>180</v>
       </c>
@@ -17323,7 +17327,7 @@
         <v>42.41</v>
       </c>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A492" t="s">
         <v>343</v>
       </c>
@@ -17352,7 +17356,7 @@
         <v>41.76</v>
       </c>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A493" t="s">
         <v>444</v>
       </c>
@@ -17381,7 +17385,7 @@
         <v>41.65</v>
       </c>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A494" t="s">
         <v>243</v>
       </c>
@@ -17410,7 +17414,7 @@
         <v>45.4</v>
       </c>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A495" t="s">
         <v>216</v>
       </c>
@@ -17439,7 +17443,7 @@
         <v>44.87</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A496" t="s">
         <v>296</v>
       </c>
@@ -17468,7 +17472,7 @@
         <v>43.06</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A497" t="s">
         <v>342</v>
       </c>
@@ -17497,7 +17501,7 @@
         <v>45.34</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A498" t="s">
         <v>174</v>
       </c>
@@ -17526,7 +17530,7 @@
         <v>41.04</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A499" t="s">
         <v>264</v>
       </c>
@@ -17555,7 +17559,7 @@
         <v>42.75</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A500" t="s">
         <v>183</v>
       </c>
@@ -17584,7 +17588,7 @@
         <v>42.03</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A501" t="s">
         <v>393</v>
       </c>
@@ -17613,7 +17617,7 @@
         <v>43.21</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A502" t="s">
         <v>404</v>
       </c>
@@ -17642,7 +17646,7 @@
         <v>42.87</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A503" t="s">
         <v>278</v>
       </c>
@@ -17671,7 +17675,7 @@
         <v>41.62</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A504" t="s">
         <v>364</v>
       </c>
@@ -17700,7 +17704,7 @@
         <v>46.76</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A505" t="s">
         <v>322</v>
       </c>
@@ -17729,7 +17733,7 @@
         <v>42.59</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A506" t="s">
         <v>325</v>
       </c>
@@ -17758,7 +17762,7 @@
         <v>41.35</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A507" t="s">
         <v>420</v>
       </c>
@@ -17787,7 +17791,7 @@
         <v>45.7</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A508" t="s">
         <v>260</v>
       </c>
@@ -17816,7 +17820,7 @@
         <v>46.81</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A509" t="s">
         <v>450</v>
       </c>
@@ -17845,7 +17849,7 @@
         <v>48.02</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A510" t="s">
         <v>323</v>
       </c>
@@ -17874,7 +17878,7 @@
         <v>46.7</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A511" t="s">
         <v>403</v>
       </c>
@@ -17903,7 +17907,7 @@
         <v>44.8</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A512" t="s">
         <v>388</v>
       </c>
@@ -17932,7 +17936,7 @@
         <v>43.76</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A513" t="s">
         <v>456</v>
       </c>
@@ -17961,7 +17965,7 @@
         <v>43.08</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A514" t="s">
         <v>328</v>
       </c>
@@ -17990,7 +17994,7 @@
         <v>46.5</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A515" t="s">
         <v>455</v>
       </c>
@@ -18019,7 +18023,7 @@
         <v>40.020000000000003</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A516" t="s">
         <v>417</v>
       </c>
@@ -18048,7 +18052,7 @@
         <v>46.15</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A517" t="s">
         <v>217</v>
       </c>
@@ -18077,7 +18081,7 @@
         <v>45.7</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A518" t="s">
         <v>350</v>
       </c>
@@ -18106,7 +18110,7 @@
         <v>38.56</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A519" t="s">
         <v>469</v>
       </c>
@@ -18135,7 +18139,7 @@
         <v>40.69</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A520" t="s">
         <v>297</v>
       </c>
@@ -18164,7 +18168,7 @@
         <v>40.36</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A521" t="s">
         <v>394</v>
       </c>
@@ -18193,7 +18197,7 @@
         <v>43.67</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A522" t="s">
         <v>252</v>
       </c>
@@ -18222,7 +18226,7 @@
         <v>47.11</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A523" t="s">
         <v>365</v>
       </c>
@@ -18251,7 +18255,7 @@
         <v>44.4</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A524" t="s">
         <v>401</v>
       </c>
@@ -18280,7 +18284,7 @@
         <v>47.36</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A525" t="s">
         <v>442</v>
       </c>
@@ -18309,7 +18313,7 @@
         <v>46.75</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A526" t="s">
         <v>440</v>
       </c>
@@ -18338,7 +18342,7 @@
         <v>47.49</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A527" t="s">
         <v>197</v>
       </c>
@@ -18367,7 +18371,7 @@
         <v>45.92</v>
       </c>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A528" t="s">
         <v>443</v>
       </c>
@@ -18396,7 +18400,7 @@
         <v>45.86</v>
       </c>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A529" t="s">
         <v>366</v>
       </c>
@@ -18425,7 +18429,7 @@
         <v>44.49</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A530" t="s">
         <v>240</v>
       </c>
@@ -18454,7 +18458,7 @@
         <v>43.77</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A531" t="s">
         <v>391</v>
       </c>
@@ -18483,7 +18487,7 @@
         <v>49.09</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A532" t="s">
         <v>470</v>
       </c>
@@ -18512,7 +18516,7 @@
         <v>50.47</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A533" t="s">
         <v>248</v>
       </c>
@@ -18541,7 +18545,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A534" t="s">
         <v>399</v>
       </c>
@@ -18570,7 +18574,7 @@
         <v>49.03</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A535" t="s">
         <v>262</v>
       </c>
@@ -18599,7 +18603,7 @@
         <v>47.4</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A536" t="s">
         <v>414</v>
       </c>
@@ -18628,7 +18632,7 @@
         <v>50.19</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A537" t="s">
         <v>223</v>
       </c>
@@ -18657,7 +18661,7 @@
         <v>48.68</v>
       </c>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A538" t="s">
         <v>224</v>
       </c>
@@ -18686,7 +18690,7 @@
         <v>47.61</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A539" t="s">
         <v>352</v>
       </c>
@@ -18715,7 +18719,7 @@
         <v>47.15</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A540" t="s">
         <v>419</v>
       </c>
@@ -18744,7 +18748,7 @@
         <v>50.28</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A541" t="s">
         <v>171</v>
       </c>
@@ -18773,7 +18777,7 @@
         <v>47.93</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A542" t="s">
         <v>251</v>
       </c>
@@ -18802,7 +18806,7 @@
         <v>50.23</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A543" t="s">
         <v>210</v>
       </c>
@@ -18831,7 +18835,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A544" t="s">
         <v>237</v>
       </c>
@@ -18860,7 +18864,7 @@
         <v>48.76</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A545" t="s">
         <v>276</v>
       </c>
@@ -18889,7 +18893,7 @@
         <v>50.02</v>
       </c>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A546" t="s">
         <v>310</v>
       </c>
@@ -18918,7 +18922,7 @@
         <v>50.39</v>
       </c>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A547" t="s">
         <v>409</v>
       </c>
@@ -18947,7 +18951,7 @@
         <v>49.33</v>
       </c>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A548" t="s">
         <v>377</v>
       </c>
@@ -18976,7 +18980,7 @@
         <v>49.19</v>
       </c>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A549" t="s">
         <v>179</v>
       </c>
@@ -19005,7 +19009,7 @@
         <v>49.71</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A550" t="s">
         <v>184</v>
       </c>
@@ -19034,7 +19038,7 @@
         <v>49.95</v>
       </c>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A551" t="s">
         <v>274</v>
       </c>
@@ -19063,7 +19067,7 @@
         <v>49.12</v>
       </c>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A552" t="s">
         <v>389</v>
       </c>
@@ -19092,7 +19096,7 @@
         <v>49.72</v>
       </c>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A553" t="s">
         <v>294</v>
       </c>
@@ -19121,7 +19125,7 @@
         <v>49.32</v>
       </c>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A554" t="s">
         <v>300</v>
       </c>
@@ -19150,7 +19154,7 @@
         <v>49.69</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A555" t="s">
         <v>227</v>
       </c>
@@ -19179,7 +19183,7 @@
         <v>50.17</v>
       </c>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A556" t="s">
         <v>357</v>
       </c>
@@ -19208,7 +19212,7 @@
         <v>49.64</v>
       </c>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A557" t="s">
         <v>187</v>
       </c>
@@ -19237,7 +19241,7 @@
         <v>48.38</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A558" t="s">
         <v>292</v>
       </c>
@@ -19266,7 +19270,7 @@
         <v>50.26</v>
       </c>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A559" t="s">
         <v>372</v>
       </c>
@@ -19295,7 +19299,7 @@
         <v>47.67</v>
       </c>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A560" t="s">
         <v>304</v>
       </c>
@@ -19324,7 +19328,7 @@
         <v>48.42</v>
       </c>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A561" t="s">
         <v>396</v>
       </c>
@@ -19353,7 +19357,7 @@
         <v>49.39</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A562" t="s">
         <v>280</v>
       </c>
@@ -19382,7 +19386,7 @@
         <v>48.56</v>
       </c>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A563" t="s">
         <v>203</v>
       </c>
@@ -19411,7 +19415,7 @@
         <v>50.51</v>
       </c>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A564" t="s">
         <v>435</v>
       </c>
@@ -19440,7 +19444,7 @@
         <v>50.81</v>
       </c>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A565" t="s">
         <v>226</v>
       </c>
@@ -19469,7 +19473,7 @@
         <v>49.52</v>
       </c>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A566" t="s">
         <v>233</v>
       </c>
@@ -19498,7 +19502,7 @@
         <v>49.27</v>
       </c>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A567" t="s">
         <v>255</v>
       </c>
@@ -19527,7 +19531,7 @@
         <v>50.31</v>
       </c>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A568" t="s">
         <v>302</v>
       </c>
@@ -19556,7 +19560,7 @@
         <v>50.13</v>
       </c>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A569" t="s">
         <v>431</v>
       </c>
@@ -19585,7 +19589,7 @@
         <v>50.25</v>
       </c>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A570" t="s">
         <v>452</v>
       </c>
@@ -19614,7 +19618,7 @@
         <v>48.79</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A571" t="s">
         <v>198</v>
       </c>
@@ -19643,7 +19647,7 @@
         <v>50.01</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A572" t="s">
         <v>200</v>
       </c>
@@ -19672,7 +19676,7 @@
         <v>49.86</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A573" t="s">
         <v>411</v>
       </c>
@@ -19701,7 +19705,7 @@
         <v>48.81</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A574" t="s">
         <v>398</v>
       </c>
@@ -19730,7 +19734,7 @@
         <v>49.84</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A575" t="s">
         <v>191</v>
       </c>
@@ -19759,7 +19763,7 @@
         <v>49.65</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A576" t="s">
         <v>238</v>
       </c>
@@ -19788,7 +19792,7 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A577" t="s">
         <v>273</v>
       </c>
@@ -19817,7 +19821,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A578" t="s">
         <v>373</v>
       </c>
@@ -19846,7 +19850,7 @@
         <v>48.14</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A579" t="s">
         <v>293</v>
       </c>
@@ -19875,7 +19879,7 @@
         <v>48.48</v>
       </c>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A580" t="s">
         <v>214</v>
       </c>
@@ -19904,7 +19908,7 @@
         <v>48.38</v>
       </c>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A581" t="s">
         <v>283</v>
       </c>
@@ -19933,7 +19937,7 @@
         <v>46.96</v>
       </c>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A582" t="s">
         <v>241</v>
       </c>
@@ -19962,7 +19966,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A583" t="s">
         <v>376</v>
       </c>
@@ -19991,7 +19995,7 @@
         <v>47.82</v>
       </c>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A584" t="s">
         <v>422</v>
       </c>
@@ -20020,7 +20024,7 @@
         <v>47.4</v>
       </c>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A585" t="s">
         <v>461</v>
       </c>
@@ -20049,7 +20053,7 @@
         <v>46.98</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A586" t="s">
         <v>196</v>
       </c>
@@ -20078,7 +20082,7 @@
         <v>48.22</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A587" t="s">
         <v>307</v>
       </c>
@@ -20107,7 +20111,7 @@
         <v>49.37</v>
       </c>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A588" t="s">
         <v>408</v>
       </c>
@@ -20136,7 +20140,7 @@
         <v>46.48</v>
       </c>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A589" t="s">
         <v>380</v>
       </c>
@@ -20165,7 +20169,7 @@
         <v>48.24</v>
       </c>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A590" t="s">
         <v>245</v>
       </c>
@@ -20194,7 +20198,7 @@
         <v>49.44</v>
       </c>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A591" t="s">
         <v>313</v>
       </c>
@@ -20223,7 +20227,7 @@
         <v>47.89</v>
       </c>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A592" t="s">
         <v>266</v>
       </c>
@@ -20252,7 +20256,7 @@
         <v>48.98</v>
       </c>
     </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A593" t="s">
         <v>178</v>
       </c>
@@ -20281,7 +20285,7 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A594" t="s">
         <v>392</v>
       </c>
@@ -20310,7 +20314,7 @@
         <v>49.39</v>
       </c>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A595" t="s">
         <v>361</v>
       </c>
@@ -20339,7 +20343,7 @@
         <v>49.76</v>
       </c>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A596" t="s">
         <v>338</v>
       </c>
@@ -20368,7 +20372,7 @@
         <v>48.23</v>
       </c>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A597" t="s">
         <v>329</v>
       </c>
@@ -20397,7 +20401,7 @@
         <v>48.08</v>
       </c>
     </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A598" t="s">
         <v>258</v>
       </c>
@@ -20426,7 +20430,7 @@
         <v>48.68</v>
       </c>
     </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A599" t="s">
         <v>397</v>
       </c>
@@ -20455,7 +20459,7 @@
         <v>46.89</v>
       </c>
     </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A600" t="s">
         <v>320</v>
       </c>
@@ -20484,7 +20488,7 @@
         <v>48.9</v>
       </c>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A601" t="s">
         <v>334</v>
       </c>
@@ -20513,7 +20517,7 @@
         <v>48.46</v>
       </c>
     </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A602" t="s">
         <v>265</v>
       </c>
@@ -20542,7 +20546,7 @@
         <v>47.79</v>
       </c>
     </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A603" t="s">
         <v>195</v>
       </c>
@@ -20571,7 +20575,7 @@
         <v>47.9</v>
       </c>
     </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A604" t="s">
         <v>368</v>
       </c>
@@ -20600,7 +20604,7 @@
         <v>48.55</v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A605" t="s">
         <v>268</v>
       </c>
@@ -20629,7 +20633,7 @@
         <v>48.07</v>
       </c>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A606" t="s">
         <v>358</v>
       </c>
@@ -20658,7 +20662,7 @@
         <v>48.11</v>
       </c>
     </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A607" t="s">
         <v>359</v>
       </c>
@@ -20687,7 +20691,7 @@
         <v>48.9</v>
       </c>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A608" t="s">
         <v>246</v>
       </c>
@@ -20716,7 +20720,7 @@
         <v>49.17</v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A609" t="s">
         <v>298</v>
       </c>
@@ -20745,7 +20749,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A610" t="s">
         <v>192</v>
       </c>
@@ -20774,7 +20778,7 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A611" t="s">
         <v>249</v>
       </c>
@@ -20803,7 +20807,7 @@
         <v>48.09</v>
       </c>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A612" t="s">
         <v>244</v>
       </c>
@@ -20832,7 +20836,7 @@
         <v>48.21</v>
       </c>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A613" t="s">
         <v>229</v>
       </c>
@@ -20861,7 +20865,7 @@
         <v>47.71</v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A614" t="s">
         <v>451</v>
       </c>
@@ -20890,7 +20894,7 @@
         <v>48.27</v>
       </c>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A615" t="s">
         <v>254</v>
       </c>
@@ -20919,7 +20923,7 @@
         <v>48.62</v>
       </c>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A616" t="s">
         <v>345</v>
       </c>
@@ -20948,7 +20952,7 @@
         <v>48.18</v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A617" t="s">
         <v>457</v>
       </c>
@@ -20977,7 +20981,7 @@
         <v>47.85</v>
       </c>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A618" t="s">
         <v>355</v>
       </c>
@@ -21006,7 +21010,7 @@
         <v>46.38</v>
       </c>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A619" t="s">
         <v>428</v>
       </c>
@@ -21035,7 +21039,7 @@
         <v>47.43</v>
       </c>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A620" t="s">
         <v>449</v>
       </c>
@@ -21064,7 +21068,7 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A621" t="s">
         <v>222</v>
       </c>
@@ -21093,7 +21097,7 @@
         <v>47.93</v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A622" t="s">
         <v>349</v>
       </c>
@@ -21122,7 +21126,7 @@
         <v>47.37</v>
       </c>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A623" t="s">
         <v>335</v>
       </c>
@@ -21151,7 +21155,7 @@
         <v>48.24</v>
       </c>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A624" t="s">
         <v>464</v>
       </c>
@@ -21180,7 +21184,7 @@
         <v>48.24</v>
       </c>
     </row>
-    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A625" t="s">
         <v>269</v>
       </c>
@@ -21209,7 +21213,7 @@
         <v>48.13</v>
       </c>
     </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A626" t="s">
         <v>446</v>
       </c>
@@ -21238,7 +21242,7 @@
         <v>46.98</v>
       </c>
     </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A627" t="s">
         <v>447</v>
       </c>
@@ -21267,7 +21271,7 @@
         <v>47.91</v>
       </c>
     </row>
-    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A628" t="s">
         <v>311</v>
       </c>
@@ -21296,7 +21300,7 @@
         <v>47.3</v>
       </c>
     </row>
-    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A629" t="s">
         <v>406</v>
       </c>
@@ -21325,7 +21329,7 @@
         <v>48.88</v>
       </c>
     </row>
-    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A630" t="s">
         <v>225</v>
       </c>
@@ -21354,7 +21358,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A631" t="s">
         <v>295</v>
       </c>
@@ -21383,7 +21387,7 @@
         <v>47.96</v>
       </c>
     </row>
-    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A632" t="s">
         <v>290</v>
       </c>
@@ -21412,7 +21416,7 @@
         <v>48.18</v>
       </c>
     </row>
-    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A633" t="s">
         <v>281</v>
       </c>
@@ -21441,7 +21445,7 @@
         <v>48.57</v>
       </c>
     </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A634" t="s">
         <v>250</v>
       </c>
@@ -21470,7 +21474,7 @@
         <v>47.69</v>
       </c>
     </row>
-    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A635" t="s">
         <v>287</v>
       </c>
@@ -21499,7 +21503,7 @@
         <v>46.84</v>
       </c>
     </row>
-    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A636" t="s">
         <v>327</v>
       </c>
@@ -21528,7 +21532,7 @@
         <v>47.96</v>
       </c>
     </row>
-    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A637" t="s">
         <v>415</v>
       </c>
@@ -21557,7 +21561,7 @@
         <v>49.03</v>
       </c>
     </row>
-    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A638" t="s">
         <v>445</v>
       </c>
@@ -21586,7 +21590,7 @@
         <v>48.11</v>
       </c>
     </row>
-    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A639" t="s">
         <v>384</v>
       </c>
@@ -21615,7 +21619,7 @@
         <v>47.46</v>
       </c>
     </row>
-    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A640" t="s">
         <v>61</v>
       </c>
@@ -21644,7 +21648,7 @@
         <v>46.51</v>
       </c>
     </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A641" t="s">
         <v>23</v>
       </c>
@@ -21673,7 +21677,7 @@
         <v>47.13</v>
       </c>
     </row>
-    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A642" t="s">
         <v>154</v>
       </c>
@@ -21702,7 +21706,7 @@
         <v>45.78</v>
       </c>
     </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A643" t="s">
         <v>74</v>
       </c>
@@ -21731,7 +21735,7 @@
         <v>48.31</v>
       </c>
     </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A644" t="s">
         <v>96</v>
       </c>
@@ -21760,7 +21764,7 @@
         <v>59.93</v>
       </c>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A645" t="s">
         <v>12</v>
       </c>
@@ -21789,7 +21793,7 @@
         <v>46.28</v>
       </c>
     </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A646" t="s">
         <v>166</v>
       </c>
@@ -21818,7 +21822,7 @@
         <v>48.15</v>
       </c>
     </row>
-    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A647" t="s">
         <v>121</v>
       </c>
@@ -21847,7 +21851,7 @@
         <v>47.66</v>
       </c>
     </row>
-    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A648" t="s">
         <v>79</v>
       </c>
@@ -21876,7 +21880,7 @@
         <v>47.64</v>
       </c>
     </row>
-    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A649" t="s">
         <v>87</v>
       </c>
@@ -21905,7 +21909,7 @@
         <v>48.12</v>
       </c>
     </row>
-    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A650" t="s">
         <v>152</v>
       </c>
@@ -21934,7 +21938,7 @@
         <v>47.73</v>
       </c>
     </row>
-    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A651" t="s">
         <v>47</v>
       </c>
@@ -21963,7 +21967,7 @@
         <v>45.05</v>
       </c>
     </row>
-    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A652" t="s">
         <v>71</v>
       </c>
@@ -21992,7 +21996,7 @@
         <v>48.25</v>
       </c>
     </row>
-    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A653" t="s">
         <v>113</v>
       </c>
@@ -22021,7 +22025,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A654" t="s">
         <v>52</v>
       </c>
@@ -22050,7 +22054,7 @@
         <v>46.24</v>
       </c>
     </row>
-    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A655" t="s">
         <v>19</v>
       </c>
@@ -22079,7 +22083,7 @@
         <v>48.46</v>
       </c>
     </row>
-    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A656" t="s">
         <v>92</v>
       </c>
@@ -22108,7 +22112,7 @@
         <v>47.27</v>
       </c>
     </row>
-    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A657" t="s">
         <v>114</v>
       </c>
@@ -22137,7 +22141,7 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A658" t="s">
         <v>95</v>
       </c>
@@ -22166,7 +22170,7 @@
         <v>45.75</v>
       </c>
     </row>
-    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A659" t="s">
         <v>78</v>
       </c>
@@ -22195,7 +22199,7 @@
         <v>49.01</v>
       </c>
     </row>
-    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A660" t="s">
         <v>85</v>
       </c>
@@ -22224,7 +22228,7 @@
         <v>48.56</v>
       </c>
     </row>
-    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A661" t="s">
         <v>141</v>
       </c>
@@ -22253,7 +22257,7 @@
         <v>49.02</v>
       </c>
     </row>
-    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A662" t="s">
         <v>116</v>
       </c>
@@ -22282,7 +22286,7 @@
         <v>47.66</v>
       </c>
     </row>
-    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A663" t="s">
         <v>126</v>
       </c>
@@ -22311,7 +22315,7 @@
         <v>47.78</v>
       </c>
     </row>
-    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A664" t="s">
         <v>81</v>
       </c>
@@ -22340,7 +22344,7 @@
         <v>47.17</v>
       </c>
     </row>
-    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A665" t="s">
         <v>168</v>
       </c>
@@ -22369,7 +22373,7 @@
         <v>53.77</v>
       </c>
     </row>
-    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A666" t="s">
         <v>118</v>
       </c>
@@ -22398,7 +22402,7 @@
         <v>46.4</v>
       </c>
     </row>
-    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A667" t="s">
         <v>150</v>
       </c>
@@ -22427,7 +22431,7 @@
         <v>47.42</v>
       </c>
     </row>
-    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A668" t="s">
         <v>88</v>
       </c>
@@ -22456,7 +22460,7 @@
         <v>47.96</v>
       </c>
     </row>
-    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A669" t="s">
         <v>127</v>
       </c>
@@ -22485,7 +22489,7 @@
         <v>47.64</v>
       </c>
     </row>
-    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A670" t="s">
         <v>103</v>
       </c>
@@ -22514,7 +22518,7 @@
         <v>49.55</v>
       </c>
     </row>
-    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A671" t="s">
         <v>16</v>
       </c>
@@ -22543,7 +22547,7 @@
         <v>46.2</v>
       </c>
     </row>
-    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A672" t="s">
         <v>70</v>
       </c>
@@ -22572,7 +22576,7 @@
         <v>51.24</v>
       </c>
     </row>
-    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A673" t="s">
         <v>151</v>
       </c>
@@ -22601,7 +22605,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A674" t="s">
         <v>162</v>
       </c>
@@ -22630,7 +22634,7 @@
         <v>45.9</v>
       </c>
     </row>
-    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A675" t="s">
         <v>17</v>
       </c>
@@ -22659,7 +22663,7 @@
         <v>46.77</v>
       </c>
     </row>
-    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A676" t="s">
         <v>57</v>
       </c>
@@ -22688,7 +22692,7 @@
         <v>50.18</v>
       </c>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A677" t="s">
         <v>65</v>
       </c>
@@ -22717,7 +22721,7 @@
         <v>46.46</v>
       </c>
     </row>
-    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A678" t="s">
         <v>163</v>
       </c>
@@ -22746,7 +22750,7 @@
         <v>47.45</v>
       </c>
     </row>
-    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A679" t="s">
         <v>59</v>
       </c>
@@ -22775,7 +22779,7 @@
         <v>58.11</v>
       </c>
     </row>
-    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A680" t="s">
         <v>122</v>
       </c>
@@ -22804,7 +22808,7 @@
         <v>45.84</v>
       </c>
     </row>
-    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A681" t="s">
         <v>136</v>
       </c>
@@ -22833,7 +22837,7 @@
         <v>47.1</v>
       </c>
     </row>
-    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A682" t="s">
         <v>22</v>
       </c>
@@ -22862,7 +22866,7 @@
         <v>47.61</v>
       </c>
     </row>
-    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A683" t="s">
         <v>56</v>
       </c>
@@ -22891,7 +22895,7 @@
         <v>47.54</v>
       </c>
     </row>
-    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A684" t="s">
         <v>99</v>
       </c>
@@ -22920,7 +22924,7 @@
         <v>47.3</v>
       </c>
     </row>
-    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A685" t="s">
         <v>101</v>
       </c>
@@ -22949,7 +22953,7 @@
         <v>49.64</v>
       </c>
     </row>
-    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A686" t="s">
         <v>153</v>
       </c>
@@ -22978,7 +22982,7 @@
         <v>45.17</v>
       </c>
     </row>
-    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A687" t="s">
         <v>35</v>
       </c>
@@ -23007,7 +23011,7 @@
         <v>50.64</v>
       </c>
     </row>
-    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A688" t="s">
         <v>36</v>
       </c>
@@ -23036,7 +23040,7 @@
         <v>43.54</v>
       </c>
     </row>
-    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A689" t="s">
         <v>24</v>
       </c>
@@ -23065,7 +23069,7 @@
         <v>49.81</v>
       </c>
     </row>
-    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A690" t="s">
         <v>64</v>
       </c>
@@ -23094,7 +23098,7 @@
         <v>53.07</v>
       </c>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A691" t="s">
         <v>80</v>
       </c>
@@ -23123,7 +23127,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A692" t="s">
         <v>142</v>
       </c>
@@ -23152,7 +23156,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A693" t="s">
         <v>32</v>
       </c>
@@ -23181,7 +23185,7 @@
         <v>50.31</v>
       </c>
     </row>
-    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A694" t="s">
         <v>128</v>
       </c>
@@ -23210,7 +23214,7 @@
         <v>49.22</v>
       </c>
     </row>
-    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A695" t="s">
         <v>86</v>
       </c>
@@ -23239,7 +23243,7 @@
         <v>47.45</v>
       </c>
     </row>
-    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A696" t="s">
         <v>132</v>
       </c>
@@ -23268,7 +23272,7 @@
         <v>50.59</v>
       </c>
     </row>
-    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A697" t="s">
         <v>124</v>
       </c>
@@ -23297,7 +23301,7 @@
         <v>50.58</v>
       </c>
     </row>
-    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A698" t="s">
         <v>38</v>
       </c>
@@ -23326,7 +23330,7 @@
         <v>50.34</v>
       </c>
     </row>
-    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A699" t="s">
         <v>45</v>
       </c>
@@ -23355,7 +23359,7 @@
         <v>48.35</v>
       </c>
     </row>
-    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A700" t="s">
         <v>164</v>
       </c>
@@ -23384,7 +23388,7 @@
         <v>49.28</v>
       </c>
     </row>
-    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A701" t="s">
         <v>62</v>
       </c>
@@ -23413,7 +23417,7 @@
         <v>46.94</v>
       </c>
     </row>
-    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A702" t="s">
         <v>119</v>
       </c>
@@ -23442,7 +23446,7 @@
         <v>49.57</v>
       </c>
     </row>
-    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A703" t="s">
         <v>160</v>
       </c>
@@ -23471,7 +23475,7 @@
         <v>48.68</v>
       </c>
     </row>
-    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A704" t="s">
         <v>83</v>
       </c>
@@ -23500,7 +23504,7 @@
         <v>48.77</v>
       </c>
     </row>
-    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A705" t="s">
         <v>147</v>
       </c>
@@ -23529,7 +23533,7 @@
         <v>44.11</v>
       </c>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A706" t="s">
         <v>48</v>
       </c>
@@ -23558,7 +23562,7 @@
         <v>50.67</v>
       </c>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A707" t="s">
         <v>167</v>
       </c>
@@ -23587,7 +23591,7 @@
         <v>48.52</v>
       </c>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A708" t="s">
         <v>90</v>
       </c>
@@ -23616,7 +23620,7 @@
         <v>44.61</v>
       </c>
     </row>
-    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A709" t="s">
         <v>26</v>
       </c>
@@ -23645,7 +23649,7 @@
         <v>48.54</v>
       </c>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A710" t="s">
         <v>159</v>
       </c>
@@ -23674,7 +23678,7 @@
         <v>47.89</v>
       </c>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A711" t="s">
         <v>40</v>
       </c>
@@ -23703,7 +23707,7 @@
         <v>43.29</v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A712" t="s">
         <v>158</v>
       </c>
@@ -23732,7 +23736,7 @@
         <v>46.83</v>
       </c>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A713" t="s">
         <v>723</v>
       </c>
@@ -23761,7 +23765,7 @@
         <v>51.19</v>
       </c>
     </row>
-    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A714" t="s">
         <v>723</v>
       </c>
@@ -23790,7 +23794,7 @@
         <v>48.79</v>
       </c>
     </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A715" t="s">
         <v>723</v>
       </c>
@@ -23820,6 +23824,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O715" xr:uid="{2373588E-8E49-42A4-9373-CC2389CBBA35}">
+    <filterColumn colId="0">
+      <customFilters>
+        <customFilter val="*ATum*"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I715">
     <sortCondition ref="A2:A715"/>
   </sortState>
